--- a/frontend/public/templates/actionfit_upload_template_v2.xlsx
+++ b/frontend/public/templates/actionfit_upload_template_v2.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M\Desktop\shopping_mall_team_project\frontend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6415494C-7A7B-44C0-9A9F-540BB1444FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AF9BD9-78B9-4B0E-B03A-FED12293E17F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="6660" windowWidth="21600" windowHeight="10905" xr2:uid="{83AE8477-E666-47AF-AE2D-BD9432332814}"/>
+    <workbookView xWindow="240" yWindow="1455" windowWidth="21360" windowHeight="12135" activeTab="1" xr2:uid="{46EB818A-E62B-42F0-8864-015BDC999ACA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,57 +37,189 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+  <si>
+    <t>노출수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클릭수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품 상세 방문수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품 찜 유저수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장바구니 유저수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품주문수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반품건수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광고과금액</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주문금액</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품단가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카테고리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스커트&gt;롱스커트</t>
+  </si>
+  <si>
+    <t>바지&gt;와이드팬츠</t>
+  </si>
+  <si>
+    <t>셔츠/남방/블라우스&gt;셔츠/남방</t>
+  </si>
+  <si>
+    <t>셔츠/남방/블라우스&gt;블라우스</t>
+  </si>
+  <si>
+    <t>티셔츠&gt;반소매티셔츠</t>
+  </si>
+  <si>
+    <t>가디건&gt;4차없음</t>
+  </si>
+  <si>
+    <t>티셔츠&gt;긴소매티셔츠</t>
+  </si>
+  <si>
+    <t>데님/청바지&gt;와이드팬츠</t>
+  </si>
+  <si>
+    <t>스커트&gt;미니스커트</t>
+  </si>
+  <si>
+    <t>원피스&gt;롱원피스</t>
+  </si>
+  <si>
+    <t>니트/스웨터&gt;라운드니트</t>
+  </si>
+  <si>
+    <t>티셔츠&gt;민소매/나시</t>
+  </si>
+  <si>
+    <t>스커트&gt;미디스커트</t>
+  </si>
+  <si>
+    <t>바지&gt;반바지</t>
+  </si>
+  <si>
+    <t>바지&gt;캐주얼바지</t>
+  </si>
+  <si>
+    <t>요가/피트니스&gt;트랙팬츠</t>
+  </si>
+  <si>
+    <t>후드/맨투맨&gt;맨투맨/스웨트셔츠</t>
+  </si>
+  <si>
+    <t>재킷&gt;재킷(그외소재)</t>
+  </si>
+  <si>
+    <t>니트/스웨터&gt;브이넥니트</t>
+  </si>
+  <si>
+    <t>원피스&gt;미니원피스</t>
+  </si>
+  <si>
+    <t>점퍼&gt;바람막이/아노락</t>
+  </si>
+  <si>
+    <t>데님/청바지&gt;부츠컷</t>
+  </si>
+  <si>
+    <t>바지&gt;슬랙스</t>
+  </si>
+  <si>
+    <t>후드/맨투맨&gt;후드집업</t>
+  </si>
+  <si>
+    <t>스커트&gt;스커트</t>
+  </si>
+  <si>
+    <t>투피스/세트&gt;팬츠세트</t>
+  </si>
+  <si>
+    <t>재킷&gt;가죽/스웨이드재킷</t>
+  </si>
+  <si>
+    <t>원피스&gt;미디원피스</t>
+  </si>
+  <si>
+    <t>니트/스웨터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>청바지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>바지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 상의</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신발</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>봄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가을</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>겨울</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>상품명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>상품ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>노출수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>클릭수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품 상세 방문수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>찜 유저수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장바구니 유저수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품주문수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>반품건수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광고과금액</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주문금액</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품단가</t>
+    <t>상품 ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>판매 사이트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카테고리 목록</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -94,7 +227,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="5" formatCode="&quot;₩&quot;#,##0;\-&quot;₩&quot;#,##0"/>
+    <numFmt numFmtId="176" formatCode="#,##0.0%;\-#,##0.0%"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,13 +247,30 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF212121"/>
+      <name val="Amazon Ember"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -129,16 +283,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFD4D4D4"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FFD4D4D4"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FFD4D4D4"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FFD4D4D4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -148,12 +302,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="5" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -488,58 +649,285 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39547F6E-4BA5-4FC9-91CD-0A49632148F5}">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC107BC5-0E7E-45FC-BA07-48E74682F7FF}">
+  <dimension ref="A1:T13"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="7" max="7" width="19.25" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="10" max="10" width="14.125" customWidth="1"/>
-    <col min="13" max="13" width="14.125" customWidth="1"/>
+    <col min="1" max="1" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:20">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="F13" s="2"/>
+      <c r="H13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="M13" s="3"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="카테고리를 재 입력하세요" promptTitle="카테고리 선택" sqref="A2:A1048576" xr:uid="{3118E3AB-AB89-4E70-ADCF-9E5428F3DD6D}">
+      <formula1>INDIRECT("Sheet2!$A$1:$A$34")</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C585C525-FA72-4E3F-A59E-896D74EE055E}">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="30.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A35">
+    <sortCondition ref="A35"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
